--- a/vdata _DxI.xlsx
+++ b/vdata _DxI.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13130" windowHeight="6110"/>
   </bookViews>
   <sheets>
     <sheet name="INFO" sheetId="9" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="78">
   <si>
     <t>Projekt</t>
   </si>
@@ -224,49 +224,43 @@
     <t>Julien</t>
   </si>
   <si>
+    <t>stud BMLA</t>
+  </si>
+  <si>
+    <t>Jelena</t>
+  </si>
+  <si>
+    <t>Oliver</t>
+  </si>
+  <si>
+    <t>Mai - Juli 2024</t>
+  </si>
+  <si>
     <t>DxI800</t>
   </si>
   <si>
-    <t>stud BMLA</t>
-  </si>
-  <si>
-    <t>Jelena</t>
-  </si>
-  <si>
-    <t>Oliver</t>
-  </si>
-  <si>
-    <t>Mai - Juli 2024</t>
-  </si>
-  <si>
-    <t>DxI800</t>
-  </si>
-  <si>
     <t>DxI9000</t>
   </si>
   <si>
     <t>Bezeichnung</t>
   </si>
   <si>
+    <t>Methode</t>
+  </si>
+  <si>
     <t>EINHEIT</t>
   </si>
   <si>
     <t>DoseUnit</t>
   </si>
   <si>
-    <t>TSH (3.IS)</t>
-  </si>
-  <si>
-    <t>mlU/l</t>
-  </si>
-  <si>
-    <t>µIU/mL</t>
-  </si>
-  <si>
-    <t>TSH 800</t>
-  </si>
-  <si>
-    <t>TSH 9000</t>
+    <t>Ferritin</t>
+  </si>
+  <si>
+    <t>µg/dl</t>
+  </si>
+  <si>
+    <t>ng/mL</t>
   </si>
 </sst>
 </file>
@@ -289,38 +283,32 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="0" tint="-0.34998626667073579"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -478,50 +466,50 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -536,15 +524,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -557,25 +545,25 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1237,202 +1225,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="17" t="str">
+        <f>DATA!C2</f>
+        <v>Ferritin</v>
+      </c>
+      <c r="C1" s="19" t="str">
+        <f>DATA!C2</f>
+        <v>Ferritin</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="str">
-        <f>DATA!D2</f>
-        <v>mlU/l</v>
-      </c>
-      <c r="C2" s="5" t="str">
+      <c r="B2" s="2" t="str">
         <f>DATA!E2</f>
-        <v>µIU/mL</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+        <v>µg/dl</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>DATA!F2</f>
+        <v>ng/mL</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="20" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="21" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="20"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="7" t="str">
+      <c r="B7" s="21" t="str">
+        <f>DATA!A1</f>
+        <v>DxI800</v>
+      </c>
+      <c r="C7" s="3" t="str">
         <f>DATA!B1</f>
         <v>DxI9000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="20"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="13"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="10"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="10"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C14" s="20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="5" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C16" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="B17" s="9"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="20"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+      <c r="B19" s="12"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="6"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="20"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1443,18 +1434,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" customWidth="1"/>
+    <col min="4" max="5" width="14.7265625" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -1483,7 +1474,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="22">
         <v>20</v>
       </c>
@@ -1525,23 +1516,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" customWidth="1"/>
+    <col min="10" max="10" width="14.54296875" customWidth="1"/>
+    <col min="11" max="11" width="17.1796875" customWidth="1"/>
+    <col min="12" max="12" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="37" t="s">
         <v>28</v>
       </c>
@@ -1579,7 +1570,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="45" t="s">
         <v>61</v>
       </c>
@@ -1601,7 +1592,7 @@
       <c r="K2" s="44"/>
       <c r="L2" s="46"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="45" t="s">
         <v>61</v>
       </c>
@@ -1623,7 +1614,7 @@
       <c r="K3" s="44"/>
       <c r="L3" s="46"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="45" t="s">
         <v>61</v>
       </c>
@@ -1645,7 +1636,7 @@
       <c r="K4" s="44"/>
       <c r="L4" s="46"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="45" t="s">
         <v>61</v>
       </c>
@@ -1667,7 +1658,7 @@
       <c r="K5" s="44"/>
       <c r="L5" s="46"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="45" t="s">
         <v>61</v>
       </c>
@@ -1689,7 +1680,7 @@
       <c r="K6" s="44"/>
       <c r="L6" s="46"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="45" t="s">
         <v>61</v>
       </c>
@@ -1711,7 +1702,7 @@
       <c r="K7" s="44"/>
       <c r="L7" s="46"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="45" t="s">
         <v>61</v>
       </c>
@@ -1733,7 +1724,7 @@
       <c r="K8" s="44"/>
       <c r="L8" s="46"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="45" t="s">
         <v>61</v>
       </c>
@@ -1755,7 +1746,7 @@
       <c r="K9" s="44"/>
       <c r="L9" s="46"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="45" t="s">
         <v>61</v>
       </c>
@@ -1777,7 +1768,7 @@
       <c r="K10" s="44"/>
       <c r="L10" s="46"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="45" t="s">
         <v>61</v>
       </c>
@@ -1799,12 +1790,12 @@
       <c r="K11" s="44"/>
       <c r="L11" s="46"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
       <c r="F23" s="52"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="23"/>
       <c r="B24" s="51"/>
       <c r="C24" s="51"/>
@@ -1812,7 +1803,7 @@
       <c r="E24" s="52"/>
       <c r="F24" s="52"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="53"/>
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
@@ -1820,7 +1811,7 @@
       <c r="E25" s="52"/>
       <c r="F25" s="52"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="30"/>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
@@ -1828,7 +1819,7 @@
       <c r="E26" s="30"/>
       <c r="F26" s="31"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="32"/>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>
@@ -1836,7 +1827,7 @@
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="35"/>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
@@ -1844,7 +1835,7 @@
       <c r="E28" s="34"/>
       <c r="F28" s="27"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="33"/>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
@@ -1852,7 +1843,7 @@
       <c r="E29" s="33"/>
       <c r="F29" s="27"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="33"/>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -1860,7 +1851,7 @@
       <c r="E30" s="33"/>
       <c r="F30" s="27"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="33"/>
       <c r="B31" s="27"/>
       <c r="C31" s="27"/>
@@ -1868,7 +1859,7 @@
       <c r="E31" s="33"/>
       <c r="F31" s="27"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="33"/>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
@@ -1876,7 +1867,7 @@
       <c r="E32" s="33"/>
       <c r="F32" s="27"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="33"/>
       <c r="B33" s="27"/>
       <c r="C33" s="27"/>
@@ -1884,7 +1875,7 @@
       <c r="E33" s="33"/>
       <c r="F33" s="27"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="33"/>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
@@ -1892,7 +1883,7 @@
       <c r="E34" s="33"/>
       <c r="F34" s="27"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="33"/>
       <c r="B35" s="27"/>
       <c r="C35" s="27"/>
@@ -1900,7 +1891,7 @@
       <c r="E35" s="33"/>
       <c r="F35" s="27"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="33"/>
       <c r="B36" s="27"/>
       <c r="C36" s="27"/>
@@ -1908,7 +1899,7 @@
       <c r="E36" s="33"/>
       <c r="F36" s="27"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="33"/>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
@@ -1916,7 +1907,7 @@
       <c r="E37" s="33"/>
       <c r="F37" s="27"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="36"/>
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
@@ -1924,7 +1915,7 @@
       <c r="E38" s="61"/>
       <c r="F38" s="25"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="36"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -1932,7 +1923,7 @@
       <c r="E39" s="61"/>
       <c r="F39" s="25"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="36"/>
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
@@ -1940,7 +1931,7 @@
       <c r="E40" s="61"/>
       <c r="F40" s="26"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
       <c r="C41" s="49"/>
@@ -1948,7 +1939,7 @@
       <c r="E41" s="49"/>
       <c r="F41" s="49"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="29"/>
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
@@ -1956,7 +1947,7 @@
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="23"/>
       <c r="B46" s="54"/>
       <c r="C46" s="54"/>
@@ -1964,7 +1955,7 @@
       <c r="E46" s="52"/>
       <c r="F46" s="52"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="23"/>
       <c r="B47" s="54"/>
       <c r="C47" s="54"/>
@@ -1972,7 +1963,7 @@
       <c r="E47" s="52"/>
       <c r="F47" s="52"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="23"/>
       <c r="B48" s="54"/>
       <c r="C48" s="54"/>
@@ -1980,7 +1971,7 @@
       <c r="E48" s="52"/>
       <c r="F48" s="52"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="23"/>
       <c r="B49" s="54"/>
       <c r="C49" s="54"/>
@@ -1988,7 +1979,7 @@
       <c r="E49" s="52"/>
       <c r="F49" s="52"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="23"/>
       <c r="B50" s="54"/>
       <c r="C50" s="54"/>
@@ -1996,7 +1987,7 @@
       <c r="E50" s="52"/>
       <c r="F50" s="52"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="23"/>
       <c r="B51" s="54"/>
       <c r="C51" s="54"/>
@@ -2004,7 +1995,7 @@
       <c r="E51" s="52"/>
       <c r="F51" s="52"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="23"/>
       <c r="B52" s="54"/>
       <c r="C52" s="54"/>
@@ -2012,7 +2003,7 @@
       <c r="E52" s="52"/>
       <c r="F52" s="52"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="23"/>
       <c r="B53" s="54"/>
       <c r="C53" s="54"/>
@@ -2020,7 +2011,7 @@
       <c r="E53" s="52"/>
       <c r="F53" s="52"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="23"/>
       <c r="B54" s="54"/>
       <c r="C54" s="54"/>
@@ -2028,7 +2019,7 @@
       <c r="E54" s="52"/>
       <c r="F54" s="52"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="23"/>
       <c r="B55" s="54"/>
       <c r="C55" s="54"/>
@@ -2036,7 +2027,7 @@
       <c r="E55" s="52"/>
       <c r="F55" s="52"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="23"/>
       <c r="B56" s="24"/>
       <c r="C56" s="24"/>
@@ -2044,7 +2035,7 @@
       <c r="E56" s="52"/>
       <c r="F56" s="52"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="23"/>
       <c r="B57" s="24"/>
       <c r="C57" s="24"/>
@@ -2052,7 +2043,7 @@
       <c r="E57" s="52"/>
       <c r="F57" s="52"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="23"/>
       <c r="B58" s="24"/>
       <c r="C58" s="24"/>
@@ -2060,7 +2051,7 @@
       <c r="E58" s="52"/>
       <c r="F58" s="52"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="23"/>
       <c r="B59" s="24"/>
       <c r="C59" s="24"/>
@@ -2068,7 +2059,7 @@
       <c r="E59" s="52"/>
       <c r="F59" s="52"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="23"/>
       <c r="B60" s="24"/>
       <c r="C60" s="24"/>
@@ -2076,7 +2067,7 @@
       <c r="E60" s="52"/>
       <c r="F60" s="52"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="23"/>
       <c r="B61" s="24"/>
       <c r="C61" s="24"/>
@@ -2084,7 +2075,7 @@
       <c r="E61" s="52"/>
       <c r="F61" s="52"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="23"/>
       <c r="B62" s="24"/>
       <c r="C62" s="24"/>
@@ -2092,7 +2083,7 @@
       <c r="E62" s="52"/>
       <c r="F62" s="52"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="23"/>
       <c r="B63" s="24"/>
       <c r="C63" s="24"/>
@@ -2100,7 +2091,7 @@
       <c r="E63" s="52"/>
       <c r="F63" s="52"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="23"/>
       <c r="B64" s="52"/>
       <c r="C64" s="52"/>
@@ -2108,7 +2099,7 @@
       <c r="E64" s="52"/>
       <c r="F64" s="52"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="23"/>
       <c r="B65" s="52"/>
       <c r="C65" s="52"/>
@@ -2116,7 +2107,7 @@
       <c r="E65" s="52"/>
       <c r="F65" s="52"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="23"/>
       <c r="B66" s="52"/>
       <c r="C66" s="52"/>
@@ -2124,7 +2115,7 @@
       <c r="E66" s="52"/>
       <c r="F66" s="52"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="23"/>
       <c r="B67" s="52"/>
       <c r="C67" s="52"/>
@@ -2132,7 +2123,7 @@
       <c r="E67" s="52"/>
       <c r="F67" s="52"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="23"/>
       <c r="B68" s="52"/>
       <c r="C68" s="52"/>
@@ -2140,7 +2131,7 @@
       <c r="E68" s="52"/>
       <c r="F68" s="52"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="23"/>
       <c r="B69" s="52"/>
       <c r="C69" s="52"/>
@@ -2148,7 +2139,7 @@
       <c r="E69" s="52"/>
       <c r="F69" s="52"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="23"/>
       <c r="B70" s="52"/>
       <c r="C70" s="52"/>
@@ -2156,7 +2147,7 @@
       <c r="E70" s="52"/>
       <c r="F70" s="52"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="23"/>
       <c r="B71" s="52"/>
       <c r="C71" s="52"/>
@@ -2164,7 +2155,7 @@
       <c r="E71" s="52"/>
       <c r="F71" s="52"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="23"/>
       <c r="B72" s="52"/>
       <c r="C72" s="52"/>
@@ -2172,7 +2163,7 @@
       <c r="E72" s="52"/>
       <c r="F72" s="52"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="23"/>
       <c r="B73" s="52"/>
       <c r="C73" s="52"/>
@@ -2197,862 +2188,1383 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E148"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F148"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="C1" t="s">
         <v>71</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="58">
-        <v>1.39</v>
+        <v>36</v>
       </c>
       <c r="B2" s="59">
-        <v>1.6519999999999999</v>
+        <v>30.6</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="D2" t="s">
-        <v>76</v>
+      <c r="D2">
+        <v>37274</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="56">
-        <v>1.47</v>
+        <v>62</v>
       </c>
       <c r="B3" s="57">
-        <v>1.5660000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="C3" t="s">
         <v>75</v>
       </c>
-      <c r="D3" t="s">
-        <v>76</v>
+      <c r="D3">
+        <v>37274</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="58">
-        <v>2.8</v>
+        <v>159</v>
       </c>
       <c r="B4" s="59">
-        <v>3.2719999999999998</v>
+        <v>157.80000000000001</v>
       </c>
       <c r="C4" t="s">
         <v>75</v>
       </c>
-      <c r="D4" t="s">
-        <v>76</v>
+      <c r="D4">
+        <v>37274</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="56">
-        <v>1.91</v>
+        <v>159</v>
       </c>
       <c r="B5" s="57">
-        <v>2.0960000000000001</v>
+        <v>230.6</v>
       </c>
       <c r="C5" t="s">
         <v>75</v>
       </c>
-      <c r="D5" t="s">
-        <v>76</v>
+      <c r="D5">
+        <v>37274</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="58">
-        <v>3.11</v>
+        <v>191</v>
       </c>
       <c r="B6" s="57">
-        <v>3.5939999999999999</v>
+        <v>176.3</v>
       </c>
       <c r="C6" t="s">
         <v>75</v>
       </c>
-      <c r="D6" t="s">
-        <v>76</v>
+      <c r="D6">
+        <v>37274</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="58">
-        <v>0.96399999999999997</v>
+        <v>48</v>
       </c>
       <c r="B7" s="57">
-        <v>1.109</v>
+        <v>43.3</v>
       </c>
       <c r="C7" t="s">
         <v>75</v>
       </c>
-      <c r="D7" t="s">
-        <v>76</v>
+      <c r="D7">
+        <v>37274</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="56">
-        <v>1.59</v>
+        <v>18</v>
       </c>
       <c r="B8" s="59">
-        <v>1.8360000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="C8" t="s">
         <v>75</v>
       </c>
-      <c r="D8" t="s">
-        <v>76</v>
+      <c r="D8">
+        <v>37274</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="58">
-        <v>2.2999999999999998</v>
+        <v>154</v>
       </c>
       <c r="B9" s="57">
-        <v>2.504</v>
+        <v>152.4</v>
       </c>
       <c r="C9" t="s">
         <v>75</v>
       </c>
-      <c r="D9" t="s">
-        <v>76</v>
+      <c r="D9">
+        <v>37274</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="56">
-        <v>0.82099999999999995</v>
+        <v>25</v>
       </c>
       <c r="B10" s="59">
-        <v>1.0309999999999999</v>
+        <v>21.3</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
       </c>
-      <c r="D10" t="s">
-        <v>76</v>
+      <c r="D10">
+        <v>37274</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="58">
-        <v>3.87</v>
+        <v>45</v>
       </c>
       <c r="B11" s="57">
-        <v>4.5750000000000002</v>
+        <v>42.3</v>
       </c>
       <c r="C11" t="s">
         <v>75</v>
       </c>
-      <c r="D11" t="s">
-        <v>76</v>
+      <c r="D11">
+        <v>37274</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="56">
-        <v>1.37</v>
+        <v>64</v>
       </c>
       <c r="B12" s="59">
-        <v>1.6140000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="C12" t="s">
         <v>75</v>
       </c>
-      <c r="D12" t="s">
-        <v>76</v>
+      <c r="D12">
+        <v>37274</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="58">
-        <v>2.82</v>
+        <v>64</v>
       </c>
       <c r="B13" s="57">
-        <v>3.266</v>
+        <v>71.2</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
       </c>
-      <c r="D13" t="s">
-        <v>76</v>
+      <c r="D13">
+        <v>37274</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="56">
-        <v>2.29</v>
+        <v>24</v>
       </c>
       <c r="B14" s="59">
-        <v>2.4340000000000002</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
         <v>75</v>
       </c>
-      <c r="D14" t="s">
-        <v>76</v>
+      <c r="D14">
+        <v>37274</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="58">
-        <v>2.1</v>
+        <v>128</v>
       </c>
       <c r="B15" s="57">
-        <v>2.4630000000000001</v>
+        <v>122.9</v>
       </c>
       <c r="C15" t="s">
         <v>75</v>
       </c>
-      <c r="D15" t="s">
-        <v>76</v>
+      <c r="D15">
+        <v>37274</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="58">
-        <v>1.41</v>
+        <v>128</v>
       </c>
       <c r="B16" s="57">
-        <v>1.623</v>
+        <v>137.80000000000001</v>
       </c>
       <c r="C16" t="s">
         <v>75</v>
       </c>
-      <c r="D16" t="s">
-        <v>76</v>
+      <c r="D16">
+        <v>37274</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="56">
-        <v>0.71899999999999997</v>
+        <v>31</v>
       </c>
       <c r="B17" s="59">
-        <v>0.83599999999999997</v>
+        <v>24.4</v>
       </c>
       <c r="C17" t="s">
         <v>75</v>
       </c>
-      <c r="D17" t="s">
-        <v>76</v>
+      <c r="D17">
+        <v>37274</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="58">
-        <v>1.65</v>
+        <v>31</v>
       </c>
       <c r="B18" s="57">
-        <v>1.794</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>75</v>
       </c>
-      <c r="D18" t="s">
-        <v>76</v>
+      <c r="D18">
+        <v>37274</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="56">
-        <v>0.73599999999999999</v>
+        <v>37</v>
       </c>
       <c r="B19" s="59">
-        <v>0.94299999999999995</v>
+        <v>38.6</v>
       </c>
       <c r="C19" t="s">
         <v>75</v>
       </c>
-      <c r="D19" t="s">
-        <v>76</v>
+      <c r="D19">
+        <v>37274</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="58">
-        <v>1.77</v>
+        <v>37</v>
       </c>
       <c r="B20" s="57">
-        <v>2.1349999999999998</v>
+        <v>0</v>
       </c>
       <c r="C20" t="s">
         <v>75</v>
       </c>
-      <c r="D20" t="s">
-        <v>76</v>
+      <c r="D20">
+        <v>37274</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="56"/>
-      <c r="B21" s="59"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="58"/>
-      <c r="B22" s="57"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="58"/>
-      <c r="B23" s="57"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="44"/>
-      <c r="B25" s="44"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="56"/>
-      <c r="B27" s="59"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="58"/>
-      <c r="B28" s="57"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="56"/>
-      <c r="B29" s="59"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="58"/>
-      <c r="B30" s="57"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="56"/>
-      <c r="B31" s="59"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="56"/>
-      <c r="B32" s="59"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="58"/>
-      <c r="B33" s="57"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="56"/>
-      <c r="B34" s="59"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="58"/>
-      <c r="B35" s="57"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="56"/>
-      <c r="B36" s="59"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="58"/>
-      <c r="B37" s="57"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="44"/>
-      <c r="B38" s="59"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="58"/>
-      <c r="B39" s="59"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="56"/>
-      <c r="B40" s="57"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="58"/>
-      <c r="B41" s="59"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="56"/>
-      <c r="B42" s="57"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="58"/>
-      <c r="B43" s="59"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="56"/>
-      <c r="B44" s="57"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="56"/>
-      <c r="B45" s="57"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="58"/>
-      <c r="B46" s="59"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="56"/>
-      <c r="B47" s="57"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="58"/>
-      <c r="B48" s="59"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="56"/>
-      <c r="B49" s="57"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="56">
+        <v>117</v>
+      </c>
+      <c r="B21" s="59">
+        <v>118.4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21">
+        <v>37274</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="58">
+        <v>117</v>
+      </c>
+      <c r="B22" s="57">
+        <v>124</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22">
+        <v>37274</v>
+      </c>
+      <c r="E22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="58">
+        <v>31</v>
+      </c>
+      <c r="B23" s="57">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="C23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23">
+        <v>37274</v>
+      </c>
+      <c r="E23" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="44">
+        <v>50</v>
+      </c>
+      <c r="B24" s="44">
+        <v>48.4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24">
+        <v>37274</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="44">
+        <v>50</v>
+      </c>
+      <c r="B25" s="44">
+        <v>52.2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25">
+        <v>37274</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="44">
+        <v>299</v>
+      </c>
+      <c r="B26" s="44">
+        <v>312</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26">
+        <v>37274</v>
+      </c>
+      <c r="E26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="56">
+        <v>1215</v>
+      </c>
+      <c r="B27" s="59">
+        <v>1174.5999999999999</v>
+      </c>
+      <c r="C27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27">
+        <v>37274</v>
+      </c>
+      <c r="E27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="58">
+        <v>1215</v>
+      </c>
+      <c r="B28" s="57">
+        <v>1224.4000000000001</v>
+      </c>
+      <c r="C28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28">
+        <v>37274</v>
+      </c>
+      <c r="E28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="56">
+        <v>9</v>
+      </c>
+      <c r="B29" s="59">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="C29" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29">
+        <v>37274</v>
+      </c>
+      <c r="E29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="58">
+        <v>9</v>
+      </c>
+      <c r="B30" s="57">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="C30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30">
+        <v>37274</v>
+      </c>
+      <c r="E30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="56">
+        <v>9</v>
+      </c>
+      <c r="B31" s="59">
+        <v>9.5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31">
+        <v>37274</v>
+      </c>
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="56">
+        <v>96</v>
+      </c>
+      <c r="B32" s="59">
+        <v>96.4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32">
+        <v>37274</v>
+      </c>
+      <c r="E32" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="58">
+        <v>202</v>
+      </c>
+      <c r="B33" s="57">
+        <v>193.4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33">
+        <v>37274</v>
+      </c>
+      <c r="E33" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="56">
+        <v>202</v>
+      </c>
+      <c r="B34" s="59">
+        <v>213.3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34">
+        <v>37274</v>
+      </c>
+      <c r="E34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="58">
+        <v>64</v>
+      </c>
+      <c r="B35" s="57">
+        <v>58.2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35">
+        <v>37274</v>
+      </c>
+      <c r="E35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="56">
+        <v>64</v>
+      </c>
+      <c r="B36" s="59">
+        <v>68.2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36">
+        <v>37274</v>
+      </c>
+      <c r="E36" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="58">
+        <v>98</v>
+      </c>
+      <c r="B37" s="57">
+        <v>91.9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37">
+        <v>37274</v>
+      </c>
+      <c r="E37" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="44">
+        <v>176</v>
+      </c>
+      <c r="B38" s="59">
+        <v>200.5</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38">
+        <v>37274</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="58">
+        <v>21</v>
+      </c>
+      <c r="B39" s="59">
+        <v>20.2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39">
+        <v>37274</v>
+      </c>
+      <c r="E39" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="56">
+        <v>28</v>
+      </c>
+      <c r="B40" s="57">
+        <v>29.9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40">
+        <v>37274</v>
+      </c>
+      <c r="E40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="58">
+        <v>116</v>
+      </c>
+      <c r="B41" s="59">
+        <v>116.3</v>
+      </c>
+      <c r="C41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41">
+        <v>37274</v>
+      </c>
+      <c r="E41" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="56">
+        <v>18</v>
+      </c>
+      <c r="B42" s="57">
+        <v>18.3</v>
+      </c>
+      <c r="C42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42">
+        <v>37274</v>
+      </c>
+      <c r="E42" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="58">
+        <v>382</v>
+      </c>
+      <c r="B43" s="59">
+        <v>381.4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43">
+        <v>37274</v>
+      </c>
+      <c r="E43" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="56">
+        <v>382</v>
+      </c>
+      <c r="B44" s="57">
+        <v>448.1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44">
+        <v>37274</v>
+      </c>
+      <c r="E44" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="56">
+        <v>48</v>
+      </c>
+      <c r="B45" s="57">
+        <v>48.6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45">
+        <v>37274</v>
+      </c>
+      <c r="E45" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="58">
+        <v>115</v>
+      </c>
+      <c r="B46" s="59">
+        <v>126.5</v>
+      </c>
+      <c r="C46" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46">
+        <v>37274</v>
+      </c>
+      <c r="E46" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="56">
+        <v>14</v>
+      </c>
+      <c r="B47" s="57">
+        <v>15.5</v>
+      </c>
+      <c r="C47" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47">
+        <v>37274</v>
+      </c>
+      <c r="E47" t="s">
+        <v>76</v>
+      </c>
+      <c r="F47" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="58">
+        <v>210</v>
+      </c>
+      <c r="B48" s="59">
+        <v>194.9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48">
+        <v>37274</v>
+      </c>
+      <c r="E48" t="s">
+        <v>76</v>
+      </c>
+      <c r="F48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="56">
+        <v>22</v>
+      </c>
+      <c r="B49" s="57">
+        <v>21.9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49">
+        <v>37274</v>
+      </c>
+      <c r="E49" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="58"/>
       <c r="B50" s="59"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="56"/>
       <c r="B51" s="57"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="58"/>
       <c r="B52" s="59"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="56"/>
       <c r="B53" s="57"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="58"/>
       <c r="B54" s="59"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="56"/>
       <c r="B55" s="57"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="58"/>
       <c r="B56" s="59"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="56"/>
       <c r="B57" s="57"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="58"/>
       <c r="B58" s="59"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="56"/>
       <c r="B59" s="57"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="58"/>
       <c r="B60" s="59"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="56"/>
       <c r="B61" s="57"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="58"/>
       <c r="B62" s="59"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="56"/>
       <c r="B63" s="57"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="58"/>
       <c r="B64" s="59"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="56"/>
       <c r="B65" s="57"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="58"/>
       <c r="B66" s="59"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="56"/>
       <c r="B67" s="57"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="58"/>
       <c r="B68" s="59"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="56"/>
       <c r="B69" s="57"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="58"/>
       <c r="B70" s="59"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="56"/>
       <c r="B71" s="57"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="58"/>
       <c r="B72" s="59"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="56"/>
       <c r="B73" s="57"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="58"/>
       <c r="B74" s="59"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="56"/>
       <c r="B75" s="57"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="58"/>
       <c r="B76" s="59"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="56"/>
       <c r="B77" s="57"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="58"/>
       <c r="B78" s="59"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="56"/>
       <c r="B79" s="57"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="58"/>
       <c r="B80" s="59"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="56"/>
       <c r="B81" s="57"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="58"/>
       <c r="B82" s="59"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="56"/>
       <c r="B83" s="57"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="58"/>
       <c r="B84" s="59"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="56"/>
       <c r="B85" s="57"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="58"/>
       <c r="B86" s="59"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="56"/>
       <c r="B87" s="57"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="58"/>
       <c r="B88" s="59"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="56"/>
       <c r="B89" s="57"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="58"/>
       <c r="B90" s="59"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="56"/>
       <c r="B91" s="57"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="58"/>
       <c r="B92" s="59"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="56"/>
       <c r="B93" s="57"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="58"/>
       <c r="B94" s="59"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="56"/>
       <c r="B95" s="57"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="58"/>
       <c r="B96" s="59"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="56"/>
       <c r="B97" s="57"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="58"/>
       <c r="B98" s="59"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="56"/>
       <c r="B99" s="57"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="58"/>
       <c r="B100" s="59"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="56"/>
       <c r="B101" s="57"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="58"/>
       <c r="B102" s="59"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="56"/>
       <c r="B103" s="57"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="58"/>
       <c r="B104" s="59"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="56"/>
       <c r="B105" s="57"/>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="58"/>
       <c r="B106" s="59"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="56"/>
       <c r="B107" s="57"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="58"/>
       <c r="B108" s="59"/>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="56"/>
       <c r="B109" s="57"/>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="58"/>
       <c r="B110" s="59"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="56"/>
       <c r="B111" s="57"/>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="58"/>
       <c r="B112" s="59"/>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="56"/>
       <c r="B113" s="57"/>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="58"/>
       <c r="B114" s="59"/>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="56"/>
       <c r="B115" s="57"/>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="58"/>
       <c r="B116" s="59"/>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="56"/>
       <c r="B117" s="57"/>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="58"/>
       <c r="B118" s="59"/>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="56"/>
       <c r="B119" s="57"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="58"/>
       <c r="B120" s="59"/>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="56"/>
       <c r="B121" s="57"/>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="58"/>
       <c r="B122" s="59"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="56"/>
       <c r="B123" s="57"/>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="58"/>
       <c r="B124" s="59"/>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="56"/>
       <c r="B125" s="57"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="58"/>
       <c r="B126" s="59"/>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="56"/>
       <c r="B127" s="57"/>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="58"/>
       <c r="B128" s="59"/>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="56"/>
       <c r="B129" s="57"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="58"/>
       <c r="B130" s="59"/>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="56"/>
       <c r="B131" s="57"/>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="58"/>
       <c r="B132" s="59"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="56"/>
       <c r="B133" s="57"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="58"/>
       <c r="B134" s="59"/>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="56"/>
       <c r="B135" s="57"/>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="58"/>
       <c r="B136" s="59"/>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="56"/>
       <c r="B137" s="57"/>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="58"/>
       <c r="B138" s="59"/>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="56"/>
       <c r="B139" s="57"/>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="58"/>
       <c r="B140" s="59"/>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="56"/>
       <c r="B141" s="57"/>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="58"/>
       <c r="B142" s="59"/>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="56"/>
       <c r="B143" s="57"/>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="58"/>
       <c r="B144" s="59"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="56"/>
       <c r="B145" s="57"/>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="58"/>
       <c r="B146" s="59"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="56"/>
       <c r="B147" s="57"/>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="60"/>
       <c r="B148" s="55"/>
     </row>

--- a/vdata _DxI.xlsx
+++ b/vdata _DxI.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_local\autoVal\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13130" windowHeight="6110"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="INFO" sheetId="9" r:id="rId1"/>
-    <sheet name="CRIT" sheetId="5" r:id="rId2"/>
-    <sheet name="PREC" sheetId="8" r:id="rId3"/>
-    <sheet name="DATA" sheetId="1" r:id="rId4"/>
+    <sheet name="INFO" sheetId="9" state="visible" r:id="rId1"/>
+    <sheet name="CRIT" sheetId="5" state="visible" r:id="rId2"/>
+    <sheet name="PREC" sheetId="8" state="visible" r:id="rId3"/>
+    <sheet name="DATA" sheetId="10" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>Projekt</t>
   </si>
@@ -236,42 +230,63 @@
     <t>Mai - Juli 2024</t>
   </si>
   <si>
-    <t>DxI800</t>
-  </si>
-  <si>
-    <t>DxI9000</t>
-  </si>
-  <si>
-    <t>Bezeichnung</t>
-  </si>
-  <si>
-    <t>Methode</t>
-  </si>
-  <si>
-    <t>EINHEIT</t>
-  </si>
-  <si>
-    <t>DoseUnit</t>
-  </si>
-  <si>
-    <t>Ferritin</t>
-  </si>
-  <si>
-    <t>µg/dl</t>
-  </si>
-  <si>
-    <t>ng/mL</t>
+    <t xml:space="preserve">DxI800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DxI9000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezeichnung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EINHEIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DoseUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferritin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µg/dl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ng/mL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einheit_800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einheit_9000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probennummer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a-Fetoprotein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSH (3.IS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mlU/l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µIU/mL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,10 +305,10 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <b/>
     </font>
     <font>
       <sz val="12"/>
@@ -343,7 +358,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -355,28 +370,22 @@
       <left style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </left>
-      <right/>
       <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </top>
       <bottom style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </top>
       <bottom style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </right>
@@ -386,119 +395,72 @@
       <bottom style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -510,15 +472,23 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -535,13 +505,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -570,7 +540,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -578,11 +548,11 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -593,44 +563,17 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
     <dxf>
@@ -922,7 +865,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabelle2" displayName="Tabelle2" ref="A1:I2" totalsRowShown="0" dataDxfId="25">
   <autoFilter ref="A1:I2"/>
   <tableColumns count="9">
@@ -940,7 +883,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabelle3" displayName="Tabelle3" ref="A1:L11" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
   <autoFilter ref="A1:L11"/>
   <tableColumns count="12">
@@ -1223,207 +1166,207 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="26.1796875" customWidth="1"/>
-    <col min="3" max="3" width="30.54296875" customWidth="1"/>
+    <col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="17" t="str">
+      <c r="B1" s="13" t="n">
         <f>DATA!C2</f>
-        <v>Ferritin</v>
-      </c>
-      <c r="C1" s="19" t="str">
+        <v>0</v>
+      </c>
+      <c r="C1" s="15" t="n">
         <f>DATA!C2</f>
-        <v>Ferritin</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="18" t="n">
         <f>DATA!E2</f>
-        <v>µg/dl</v>
-      </c>
-      <c r="C2" s="2" t="str">
+        <v>0</v>
+      </c>
+      <c r="C2" s="18" t="n">
         <f>DATA!F2</f>
-        <v>ng/mL</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="19" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="14" t="s">
+    <row r="4">
+      <c r="A4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="15" t="s">
+    <row r="5">
+      <c r="A5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="17" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
+    <row r="6">
+      <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="20"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="15" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="21" t="str">
+      <c r="B7" s="17" t="n">
         <f>DATA!A1</f>
-        <v>DxI800</v>
-      </c>
-      <c r="C7" s="3" t="str">
+        <v>0</v>
+      </c>
+      <c r="C7" s="19" t="n">
         <f>DATA!B1</f>
-        <v>DxI9000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="20"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
+      <c r="B8" s="21"/>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="10"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="15" t="s">
+    <row r="13">
+      <c r="A13" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="19" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
+    <row r="14">
+      <c r="A14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
+    <row r="15">
+      <c r="A15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="14" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="19"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="16" t="s">
+    <row r="17">
+      <c r="A17" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="14" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="19"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="20"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="15" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
+      <c r="B19" s="10"/>
+      <c r="C19" s="19"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="20"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="15" t="s">
+      <c r="B20" s="7"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1432,20 +1375,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.81640625" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" customWidth="1"/>
-    <col min="4" max="5" width="14.7265625" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" customWidth="1"/>
-    <col min="9" max="9" width="12.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="13" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -1474,32 +1418,32 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="22">
+    <row r="2">
+      <c r="A2" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="22" t="n">
         <v>0.95</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="22" t="n">
         <v>0.85</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="22" t="n">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="22" t="n">
         <v>4.5</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="22" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -1508,31 +1452,31 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" customWidth="1"/>
-    <col min="2" max="2" width="17.1796875" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" customWidth="1"/>
-    <col min="4" max="4" width="16.7265625" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" customWidth="1"/>
-    <col min="9" max="9" width="11.7265625" customWidth="1"/>
-    <col min="10" max="10" width="14.54296875" customWidth="1"/>
-    <col min="11" max="11" width="17.1796875" customWidth="1"/>
-    <col min="12" max="12" width="11.7265625" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="14.54296875" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="17.1796875" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="11.7265625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>28</v>
       </c>
@@ -1570,7 +1514,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="45" t="s">
         <v>61</v>
       </c>
@@ -1592,7 +1536,7 @@
       <c r="K2" s="44"/>
       <c r="L2" s="46"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="45" t="s">
         <v>61</v>
       </c>
@@ -1614,7 +1558,7 @@
       <c r="K3" s="44"/>
       <c r="L3" s="46"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="45" t="s">
         <v>61</v>
       </c>
@@ -1636,7 +1580,7 @@
       <c r="K4" s="44"/>
       <c r="L4" s="46"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="45" t="s">
         <v>61</v>
       </c>
@@ -1658,7 +1602,7 @@
       <c r="K5" s="44"/>
       <c r="L5" s="46"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="45" t="s">
         <v>61</v>
       </c>
@@ -1680,7 +1624,7 @@
       <c r="K6" s="44"/>
       <c r="L6" s="46"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="45" t="s">
         <v>61</v>
       </c>
@@ -1702,7 +1646,7 @@
       <c r="K7" s="44"/>
       <c r="L7" s="46"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="45" t="s">
         <v>61</v>
       </c>
@@ -1724,7 +1668,7 @@
       <c r="K8" s="44"/>
       <c r="L8" s="46"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="45" t="s">
         <v>61</v>
       </c>
@@ -1746,7 +1690,7 @@
       <c r="K9" s="44"/>
       <c r="L9" s="46"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="45" t="s">
         <v>61</v>
       </c>
@@ -1768,7 +1712,7 @@
       <c r="K10" s="44"/>
       <c r="L10" s="46"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="45" t="s">
         <v>61</v>
       </c>
@@ -1790,12 +1734,12 @@
       <c r="K11" s="44"/>
       <c r="L11" s="46"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
       <c r="F23" s="52"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="23"/>
       <c r="B24" s="51"/>
       <c r="C24" s="51"/>
@@ -1803,7 +1747,7 @@
       <c r="E24" s="52"/>
       <c r="F24" s="52"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" s="53"/>
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
@@ -1811,7 +1755,7 @@
       <c r="E25" s="52"/>
       <c r="F25" s="52"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="30"/>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
@@ -1819,7 +1763,7 @@
       <c r="E26" s="30"/>
       <c r="F26" s="31"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="32"/>
       <c r="B27" s="32"/>
       <c r="C27" s="32"/>
@@ -1827,7 +1771,7 @@
       <c r="E27" s="32"/>
       <c r="F27" s="32"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="35"/>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
@@ -1835,7 +1779,7 @@
       <c r="E28" s="34"/>
       <c r="F28" s="27"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="33"/>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
@@ -1843,7 +1787,7 @@
       <c r="E29" s="33"/>
       <c r="F29" s="27"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="33"/>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -1851,7 +1795,7 @@
       <c r="E30" s="33"/>
       <c r="F30" s="27"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="33"/>
       <c r="B31" s="27"/>
       <c r="C31" s="27"/>
@@ -1859,7 +1803,7 @@
       <c r="E31" s="33"/>
       <c r="F31" s="27"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="33"/>
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
@@ -1867,7 +1811,7 @@
       <c r="E32" s="33"/>
       <c r="F32" s="27"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="33"/>
       <c r="B33" s="27"/>
       <c r="C33" s="27"/>
@@ -1875,7 +1819,7 @@
       <c r="E33" s="33"/>
       <c r="F33" s="27"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="33"/>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
@@ -1883,7 +1827,7 @@
       <c r="E34" s="33"/>
       <c r="F34" s="27"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="33"/>
       <c r="B35" s="27"/>
       <c r="C35" s="27"/>
@@ -1891,7 +1835,7 @@
       <c r="E35" s="33"/>
       <c r="F35" s="27"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="33"/>
       <c r="B36" s="27"/>
       <c r="C36" s="27"/>
@@ -1899,7 +1843,7 @@
       <c r="E36" s="33"/>
       <c r="F36" s="27"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37" s="33"/>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
@@ -1907,31 +1851,31 @@
       <c r="E37" s="33"/>
       <c r="F37" s="27"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="36"/>
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
       <c r="F38" s="25"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39" s="36"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
       <c r="F39" s="25"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40" s="36"/>
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
       <c r="F40" s="26"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="49"/>
       <c r="B41" s="49"/>
       <c r="C41" s="49"/>
@@ -1939,7 +1883,7 @@
       <c r="E41" s="49"/>
       <c r="F41" s="49"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42" s="29"/>
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
@@ -1947,7 +1891,7 @@
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46" s="23"/>
       <c r="B46" s="54"/>
       <c r="C46" s="54"/>
@@ -1955,7 +1899,7 @@
       <c r="E46" s="52"/>
       <c r="F46" s="52"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47" s="23"/>
       <c r="B47" s="54"/>
       <c r="C47" s="54"/>
@@ -1963,7 +1907,7 @@
       <c r="E47" s="52"/>
       <c r="F47" s="52"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48" s="23"/>
       <c r="B48" s="54"/>
       <c r="C48" s="54"/>
@@ -1971,7 +1915,7 @@
       <c r="E48" s="52"/>
       <c r="F48" s="52"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49" s="23"/>
       <c r="B49" s="54"/>
       <c r="C49" s="54"/>
@@ -1979,7 +1923,7 @@
       <c r="E49" s="52"/>
       <c r="F49" s="52"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50" s="23"/>
       <c r="B50" s="54"/>
       <c r="C50" s="54"/>
@@ -1987,7 +1931,7 @@
       <c r="E50" s="52"/>
       <c r="F50" s="52"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51">
       <c r="A51" s="23"/>
       <c r="B51" s="54"/>
       <c r="C51" s="54"/>
@@ -1995,7 +1939,7 @@
       <c r="E51" s="52"/>
       <c r="F51" s="52"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52" s="23"/>
       <c r="B52" s="54"/>
       <c r="C52" s="54"/>
@@ -2003,7 +1947,7 @@
       <c r="E52" s="52"/>
       <c r="F52" s="52"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53" s="23"/>
       <c r="B53" s="54"/>
       <c r="C53" s="54"/>
@@ -2011,7 +1955,7 @@
       <c r="E53" s="52"/>
       <c r="F53" s="52"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54" s="23"/>
       <c r="B54" s="54"/>
       <c r="C54" s="54"/>
@@ -2019,7 +1963,7 @@
       <c r="E54" s="52"/>
       <c r="F54" s="52"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55" s="23"/>
       <c r="B55" s="54"/>
       <c r="C55" s="54"/>
@@ -2027,7 +1971,7 @@
       <c r="E55" s="52"/>
       <c r="F55" s="52"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56">
       <c r="A56" s="23"/>
       <c r="B56" s="24"/>
       <c r="C56" s="24"/>
@@ -2035,7 +1979,7 @@
       <c r="E56" s="52"/>
       <c r="F56" s="52"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57" s="23"/>
       <c r="B57" s="24"/>
       <c r="C57" s="24"/>
@@ -2043,7 +1987,7 @@
       <c r="E57" s="52"/>
       <c r="F57" s="52"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58" s="23"/>
       <c r="B58" s="24"/>
       <c r="C58" s="24"/>
@@ -2051,7 +1995,7 @@
       <c r="E58" s="52"/>
       <c r="F58" s="52"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59" s="23"/>
       <c r="B59" s="24"/>
       <c r="C59" s="24"/>
@@ -2059,7 +2003,7 @@
       <c r="E59" s="52"/>
       <c r="F59" s="52"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60" s="23"/>
       <c r="B60" s="24"/>
       <c r="C60" s="24"/>
@@ -2067,7 +2011,7 @@
       <c r="E60" s="52"/>
       <c r="F60" s="52"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61" s="23"/>
       <c r="B61" s="24"/>
       <c r="C61" s="24"/>
@@ -2075,7 +2019,7 @@
       <c r="E61" s="52"/>
       <c r="F61" s="52"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62" s="23"/>
       <c r="B62" s="24"/>
       <c r="C62" s="24"/>
@@ -2083,7 +2027,7 @@
       <c r="E62" s="52"/>
       <c r="F62" s="52"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63" s="23"/>
       <c r="B63" s="24"/>
       <c r="C63" s="24"/>
@@ -2091,7 +2035,7 @@
       <c r="E63" s="52"/>
       <c r="F63" s="52"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64" s="23"/>
       <c r="B64" s="52"/>
       <c r="C64" s="52"/>
@@ -2099,7 +2043,7 @@
       <c r="E64" s="52"/>
       <c r="F64" s="52"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65" s="23"/>
       <c r="B65" s="52"/>
       <c r="C65" s="52"/>
@@ -2107,7 +2051,7 @@
       <c r="E65" s="52"/>
       <c r="F65" s="52"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66">
       <c r="A66" s="23"/>
       <c r="B66" s="52"/>
       <c r="C66" s="52"/>
@@ -2115,7 +2059,7 @@
       <c r="E66" s="52"/>
       <c r="F66" s="52"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67" s="23"/>
       <c r="B67" s="52"/>
       <c r="C67" s="52"/>
@@ -2123,7 +2067,7 @@
       <c r="E67" s="52"/>
       <c r="F67" s="52"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68">
       <c r="A68" s="23"/>
       <c r="B68" s="52"/>
       <c r="C68" s="52"/>
@@ -2131,7 +2075,7 @@
       <c r="E68" s="52"/>
       <c r="F68" s="52"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69">
       <c r="A69" s="23"/>
       <c r="B69" s="52"/>
       <c r="C69" s="52"/>
@@ -2139,7 +2083,7 @@
       <c r="E69" s="52"/>
       <c r="F69" s="52"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70">
       <c r="A70" s="23"/>
       <c r="B70" s="52"/>
       <c r="C70" s="52"/>
@@ -2147,7 +2091,7 @@
       <c r="E70" s="52"/>
       <c r="F70" s="52"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71" s="23"/>
       <c r="B71" s="52"/>
       <c r="C71" s="52"/>
@@ -2155,7 +2099,7 @@
       <c r="E71" s="52"/>
       <c r="F71" s="52"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72">
       <c r="A72" s="23"/>
       <c r="B72" s="52"/>
       <c r="C72" s="52"/>
@@ -2163,7 +2107,7 @@
       <c r="E72" s="52"/>
       <c r="F72" s="52"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73" s="23"/>
       <c r="B73" s="52"/>
       <c r="C73" s="52"/>
@@ -2181,25 +2125,21 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F148"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.453125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" t="s">
         <v>70</v>
       </c>
       <c r="C1" t="s">
@@ -2209,23 +2149,26 @@
         <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="58">
+        <v>79</v>
+      </c>
+      <c r="G1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>36</v>
       </c>
-      <c r="B2" s="59">
+      <c r="B2" t="n">
         <v>30.6</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>37274</v>
       </c>
       <c r="E2" t="s">
@@ -2234,18 +2177,21 @@
       <c r="F2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="56">
+      <c r="G2" t="n">
+        <v>2455289666</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>62</v>
       </c>
-      <c r="B3" s="57">
+      <c r="B3" t="n">
         <v>65.3</v>
       </c>
       <c r="C3" t="s">
         <v>75</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>37274</v>
       </c>
       <c r="E3" t="s">
@@ -2254,18 +2200,21 @@
       <c r="F3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="58">
+      <c r="G3" t="n">
+        <v>2455295646</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>159</v>
       </c>
-      <c r="B4" s="59">
-        <v>157.80000000000001</v>
+      <c r="B4" t="n">
+        <v>157.8</v>
       </c>
       <c r="C4" t="s">
         <v>75</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>37274</v>
       </c>
       <c r="E4" t="s">
@@ -2274,18 +2223,21 @@
       <c r="F4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="56">
+      <c r="G4" t="n">
+        <v>2455295705</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>159</v>
       </c>
-      <c r="B5" s="57">
+      <c r="B5" t="n">
         <v>230.6</v>
       </c>
       <c r="C5" t="s">
         <v>75</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>37274</v>
       </c>
       <c r="E5" t="s">
@@ -2294,18 +2246,21 @@
       <c r="F5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="58">
+      <c r="G5" t="n">
+        <v>2455295705</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>191</v>
       </c>
-      <c r="B6" s="57">
+      <c r="B6" t="n">
         <v>176.3</v>
       </c>
       <c r="C6" t="s">
         <v>75</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>37274</v>
       </c>
       <c r="E6" t="s">
@@ -2314,18 +2269,21 @@
       <c r="F6" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="58">
+      <c r="G6" t="n">
+        <v>2455295786</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>48</v>
       </c>
-      <c r="B7" s="57">
+      <c r="B7" t="n">
         <v>43.3</v>
       </c>
       <c r="C7" t="s">
         <v>75</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>37274</v>
       </c>
       <c r="E7" t="s">
@@ -2334,18 +2292,21 @@
       <c r="F7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="56">
+      <c r="G7" t="n">
+        <v>2455296909</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>18</v>
       </c>
-      <c r="B8" s="59">
+      <c r="B8" t="n">
         <v>17.2</v>
       </c>
       <c r="C8" t="s">
         <v>75</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>37274</v>
       </c>
       <c r="E8" t="s">
@@ -2354,18 +2315,21 @@
       <c r="F8" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="58">
+      <c r="G8" t="n">
+        <v>2455296997</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>154</v>
       </c>
-      <c r="B9" s="57">
+      <c r="B9" t="n">
         <v>152.4</v>
       </c>
       <c r="C9" t="s">
         <v>75</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>37274</v>
       </c>
       <c r="E9" t="s">
@@ -2374,18 +2338,21 @@
       <c r="F9" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="56">
+      <c r="G9" t="n">
+        <v>2455291803</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>25</v>
       </c>
-      <c r="B10" s="59">
+      <c r="B10" t="n">
         <v>21.3</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>37274</v>
       </c>
       <c r="E10" t="s">
@@ -2394,18 +2361,21 @@
       <c r="F10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="58">
+      <c r="G10" t="n">
+        <v>2455291807</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>45</v>
       </c>
-      <c r="B11" s="57">
+      <c r="B11" t="n">
         <v>42.3</v>
       </c>
       <c r="C11" t="s">
         <v>75</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>37274</v>
       </c>
       <c r="E11" t="s">
@@ -2414,18 +2384,21 @@
       <c r="F11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="56">
+      <c r="G11" t="n">
+        <v>2455296400</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>64</v>
       </c>
-      <c r="B12" s="59">
+      <c r="B12" t="n">
         <v>65.2</v>
       </c>
       <c r="C12" t="s">
         <v>75</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>37274</v>
       </c>
       <c r="E12" t="s">
@@ -2434,18 +2407,21 @@
       <c r="F12" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="58">
+      <c r="G12" t="n">
+        <v>2455296716</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>64</v>
       </c>
-      <c r="B13" s="57">
+      <c r="B13" t="n">
         <v>71.2</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>37274</v>
       </c>
       <c r="E13" t="s">
@@ -2454,18 +2430,21 @@
       <c r="F13" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="56">
+      <c r="G13" t="n">
+        <v>2455296716</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>24</v>
       </c>
-      <c r="B14" s="59">
+      <c r="B14" t="n">
         <v>22</v>
       </c>
       <c r="C14" t="s">
         <v>75</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>37274</v>
       </c>
       <c r="E14" t="s">
@@ -2474,18 +2453,21 @@
       <c r="F14" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="58">
+      <c r="G14" t="n">
+        <v>2455296724</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>128</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" t="n">
         <v>122.9</v>
       </c>
       <c r="C15" t="s">
         <v>75</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>37274</v>
       </c>
       <c r="E15" t="s">
@@ -2494,18 +2476,21 @@
       <c r="F15" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="58">
+      <c r="G15" t="n">
+        <v>2455297996</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>128</v>
       </c>
-      <c r="B16" s="57">
-        <v>137.80000000000001</v>
+      <c r="B16" t="n">
+        <v>137.8</v>
       </c>
       <c r="C16" t="s">
         <v>75</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>37274</v>
       </c>
       <c r="E16" t="s">
@@ -2514,18 +2499,21 @@
       <c r="F16" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="56">
+      <c r="G16" t="n">
+        <v>2455297996</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>31</v>
       </c>
-      <c r="B17" s="59">
+      <c r="B17" t="n">
         <v>24.4</v>
       </c>
       <c r="C17" t="s">
         <v>75</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>37274</v>
       </c>
       <c r="E17" t="s">
@@ -2534,18 +2522,21 @@
       <c r="F17" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="58">
+      <c r="G17" t="n">
+        <v>2455297709</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>31</v>
       </c>
-      <c r="B18" s="57">
+      <c r="B18" t="n">
         <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>75</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>37274</v>
       </c>
       <c r="E18" t="s">
@@ -2554,18 +2545,21 @@
       <c r="F18" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="56">
+      <c r="G18" t="n">
+        <v>2455297709</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>37</v>
       </c>
-      <c r="B19" s="59">
+      <c r="B19" t="n">
         <v>38.6</v>
       </c>
       <c r="C19" t="s">
         <v>75</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>37274</v>
       </c>
       <c r="E19" t="s">
@@ -2574,1003 +2568,1829 @@
       <c r="F19" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="58">
+      <c r="G19" t="n">
+        <v>2455297857</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>117</v>
+      </c>
+      <c r="B20" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2455297881</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>117</v>
+      </c>
+      <c r="B21" t="n">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2455297881</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>31</v>
+      </c>
+      <c r="B22" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2455298010</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>31</v>
+      </c>
+      <c r="B23" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E23" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2455298010</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>50</v>
+      </c>
+      <c r="B24" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2455298512</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>50</v>
+      </c>
+      <c r="B25" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2455298512</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>299</v>
+      </c>
+      <c r="B26" t="n">
+        <v>312</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2455298566</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>299</v>
+      </c>
+      <c r="B27" t="n">
+        <v>326.5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2455298566</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>37</v>
       </c>
-      <c r="B20" s="57">
-        <v>0</v>
-      </c>
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20">
-        <v>37274</v>
-      </c>
-      <c r="E20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="56">
-        <v>117</v>
-      </c>
-      <c r="B21" s="59">
-        <v>118.4</v>
-      </c>
-      <c r="C21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21">
-        <v>37274</v>
-      </c>
-      <c r="E21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="58">
-        <v>117</v>
-      </c>
-      <c r="B22" s="57">
-        <v>124</v>
-      </c>
-      <c r="C22" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22">
-        <v>37274</v>
-      </c>
-      <c r="E22" t="s">
-        <v>76</v>
-      </c>
-      <c r="F22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="58">
+      <c r="B28" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2455244232</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>37</v>
+      </c>
+      <c r="B29" t="n">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2455244232</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1174.6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2455299013</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1224.4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2455299013</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E32" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2455291901</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E33" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2455291901</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2455291920</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>96</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96.4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2455297358</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>202</v>
+      </c>
+      <c r="B36" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E36" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2455297367</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>202</v>
+      </c>
+      <c r="B37" t="n">
+        <v>213.3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E37" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2455297367</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>64</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2455297376</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>64</v>
+      </c>
+      <c r="B39" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E39" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2455297376</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>98</v>
+      </c>
+      <c r="B40" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="C40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2455294218</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>98</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E41" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2455294218</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>98</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91.9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E42" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2455294218</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>20</v>
+      </c>
+      <c r="B43" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E43" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" t="s">
+        <v>77</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2455297707</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>118</v>
+      </c>
+      <c r="B44" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E44" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" t="s">
+        <v>77</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2455297778</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>176</v>
+      </c>
+      <c r="B45" t="n">
+        <v>192.1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E45" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" t="s">
+        <v>77</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2455297780</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>176</v>
+      </c>
+      <c r="B46" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="C46" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E46" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2455297780</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>21</v>
+      </c>
+      <c r="B47" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E47" t="s">
+        <v>76</v>
+      </c>
+      <c r="F47" t="s">
+        <v>77</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2455298981</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>28</v>
+      </c>
+      <c r="B48" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E48" t="s">
+        <v>76</v>
+      </c>
+      <c r="F48" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2455299149</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>116</v>
+      </c>
+      <c r="B49" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E49" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2455299172</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>18</v>
+      </c>
+      <c r="B50" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E50" t="s">
+        <v>76</v>
+      </c>
+      <c r="F50" t="s">
+        <v>77</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2455299183</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>382</v>
+      </c>
+      <c r="B51" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F51" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2455299207</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>382</v>
+      </c>
+      <c r="B52" t="n">
+        <v>389.6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E52" t="s">
+        <v>76</v>
+      </c>
+      <c r="F52" t="s">
+        <v>77</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2455299207</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>382</v>
+      </c>
+      <c r="B53" t="n">
+        <v>423.1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E53" t="s">
+        <v>76</v>
+      </c>
+      <c r="F53" t="s">
+        <v>77</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2455299207</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>382</v>
+      </c>
+      <c r="B54" t="n">
+        <v>448.1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>75</v>
+      </c>
+      <c r="D54" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E54" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54" t="s">
+        <v>77</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2455299207</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E55" t="s">
+        <v>76</v>
+      </c>
+      <c r="F55" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2455299226</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>115</v>
+      </c>
+      <c r="B56" t="n">
+        <v>125</v>
+      </c>
+      <c r="C56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E56" t="s">
+        <v>76</v>
+      </c>
+      <c r="F56" t="s">
+        <v>77</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2455299447</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>115</v>
+      </c>
+      <c r="B57" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="C57" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E57" t="s">
+        <v>76</v>
+      </c>
+      <c r="F57" t="s">
+        <v>77</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2455299447</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>14</v>
+      </c>
+      <c r="B58" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C58" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E58" t="s">
+        <v>76</v>
+      </c>
+      <c r="F58" t="s">
+        <v>77</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2455299465</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>210</v>
+      </c>
+      <c r="B59" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="C59" t="s">
+        <v>75</v>
+      </c>
+      <c r="D59" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E59" t="s">
+        <v>76</v>
+      </c>
+      <c r="F59" t="s">
+        <v>77</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2455299470</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>45</v>
+      </c>
+      <c r="B60" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E60" t="s">
+        <v>76</v>
+      </c>
+      <c r="F60" t="s">
+        <v>77</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2455299486</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>45</v>
+      </c>
+      <c r="B61" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E61" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" t="s">
+        <v>77</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2455299486</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>22</v>
+      </c>
+      <c r="B62" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E62" t="s">
+        <v>76</v>
+      </c>
+      <c r="F62" t="s">
+        <v>77</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2455299488</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>36</v>
+      </c>
+      <c r="B63" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="C63" t="s">
+        <v>75</v>
+      </c>
+      <c r="D63" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E63" t="s">
+        <v>76</v>
+      </c>
+      <c r="F63" t="s">
+        <v>77</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2455299818</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>14</v>
+      </c>
+      <c r="B64" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C64" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E64" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64" t="s">
+        <v>77</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2455299821</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>14</v>
+      </c>
+      <c r="B65" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C65" t="s">
+        <v>75</v>
+      </c>
+      <c r="D65" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E65" t="s">
+        <v>76</v>
+      </c>
+      <c r="F65" t="s">
+        <v>77</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2455299821</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>207</v>
+      </c>
+      <c r="B66" t="n">
+        <v>196.2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E66" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66" t="s">
+        <v>77</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2455257447</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129</v>
+      </c>
+      <c r="B67" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E67" t="s">
+        <v>76</v>
+      </c>
+      <c r="F67" t="s">
+        <v>77</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2455387617</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>29</v>
+      </c>
+      <c r="B68" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E68" t="s">
+        <v>76</v>
+      </c>
+      <c r="F68" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2455387944</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>29</v>
+      </c>
+      <c r="B69" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>75</v>
+      </c>
+      <c r="D69" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E69" t="s">
+        <v>76</v>
+      </c>
+      <c r="F69" t="s">
+        <v>77</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2455387944</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>110</v>
+      </c>
+      <c r="B70" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>75</v>
+      </c>
+      <c r="D70" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E70" t="s">
+        <v>76</v>
+      </c>
+      <c r="F70" t="s">
+        <v>77</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2455387635</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B71" t="n">
+        <v>886.5</v>
+      </c>
+      <c r="C71" t="s">
+        <v>75</v>
+      </c>
+      <c r="D71" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E71" t="s">
+        <v>76</v>
+      </c>
+      <c r="F71" t="s">
+        <v>77</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2455387878</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B72" t="n">
+        <v>945</v>
+      </c>
+      <c r="C72" t="s">
+        <v>75</v>
+      </c>
+      <c r="D72" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E72" t="s">
+        <v>76</v>
+      </c>
+      <c r="F72" t="s">
+        <v>77</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2455387878</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B73" t="n">
+        <v>972.4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>75</v>
+      </c>
+      <c r="D73" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E73" t="s">
+        <v>76</v>
+      </c>
+      <c r="F73" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2455387878</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>39</v>
+      </c>
+      <c r="B74" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="C74" t="s">
+        <v>75</v>
+      </c>
+      <c r="D74" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E74" t="s">
+        <v>76</v>
+      </c>
+      <c r="F74" t="s">
+        <v>77</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2455387884</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>13</v>
+      </c>
+      <c r="B75" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="C75" t="s">
+        <v>75</v>
+      </c>
+      <c r="D75" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E75" t="s">
+        <v>76</v>
+      </c>
+      <c r="F75" t="s">
+        <v>77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2455387886</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125</v>
+      </c>
+      <c r="B76" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>75</v>
+      </c>
+      <c r="D76" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E76" t="s">
+        <v>76</v>
+      </c>
+      <c r="F76" t="s">
+        <v>77</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2455387887</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125</v>
+      </c>
+      <c r="B77" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="C77" t="s">
+        <v>75</v>
+      </c>
+      <c r="D77" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E77" t="s">
+        <v>76</v>
+      </c>
+      <c r="F77" t="s">
+        <v>77</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2455387887</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>815</v>
+      </c>
+      <c r="B78" t="n">
+        <v>732.2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>75</v>
+      </c>
+      <c r="D78" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E78" t="s">
+        <v>76</v>
+      </c>
+      <c r="F78" t="s">
+        <v>77</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2455388158</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>207</v>
+      </c>
+      <c r="B79" t="n">
+        <v>209</v>
+      </c>
+      <c r="C79" t="s">
+        <v>75</v>
+      </c>
+      <c r="D79" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E79" t="s">
+        <v>76</v>
+      </c>
+      <c r="F79" t="s">
+        <v>77</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2455388015</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>207</v>
+      </c>
+      <c r="B80" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="C80" t="s">
+        <v>75</v>
+      </c>
+      <c r="D80" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E80" t="s">
+        <v>76</v>
+      </c>
+      <c r="F80" t="s">
+        <v>77</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2455388015</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>45</v>
+      </c>
+      <c r="B81" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="C81" t="s">
+        <v>75</v>
+      </c>
+      <c r="D81" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E81" t="s">
+        <v>76</v>
+      </c>
+      <c r="F81" t="s">
+        <v>77</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2455388017</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>45</v>
+      </c>
+      <c r="B82" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="C82" t="s">
+        <v>75</v>
+      </c>
+      <c r="D82" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E82" t="s">
+        <v>76</v>
+      </c>
+      <c r="F82" t="s">
+        <v>77</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2455388017</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
         <v>31</v>
       </c>
-      <c r="B23" s="57">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="C23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23">
-        <v>37274</v>
-      </c>
-      <c r="E23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="44">
-        <v>50</v>
-      </c>
-      <c r="B24" s="44">
-        <v>48.4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24">
-        <v>37274</v>
-      </c>
-      <c r="E24" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="44">
-        <v>50</v>
-      </c>
-      <c r="B25" s="44">
-        <v>52.2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25">
-        <v>37274</v>
-      </c>
-      <c r="E25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="44">
-        <v>299</v>
-      </c>
-      <c r="B26" s="44">
-        <v>312</v>
-      </c>
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26">
-        <v>37274</v>
-      </c>
-      <c r="E26" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="56">
-        <v>1215</v>
-      </c>
-      <c r="B27" s="59">
-        <v>1174.5999999999999</v>
-      </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27">
-        <v>37274</v>
-      </c>
-      <c r="E27" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="58">
-        <v>1215</v>
-      </c>
-      <c r="B28" s="57">
-        <v>1224.4000000000001</v>
-      </c>
-      <c r="C28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28">
-        <v>37274</v>
-      </c>
-      <c r="E28" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="56">
-        <v>9</v>
-      </c>
-      <c r="B29" s="59">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="C29" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29">
-        <v>37274</v>
-      </c>
-      <c r="E29" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="58">
-        <v>9</v>
-      </c>
-      <c r="B30" s="57">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="C30" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30">
-        <v>37274</v>
-      </c>
-      <c r="E30" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="56">
-        <v>9</v>
-      </c>
-      <c r="B31" s="59">
-        <v>9.5</v>
-      </c>
-      <c r="C31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31">
-        <v>37274</v>
-      </c>
-      <c r="E31" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="56">
-        <v>96</v>
-      </c>
-      <c r="B32" s="59">
-        <v>96.4</v>
-      </c>
-      <c r="C32" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32">
-        <v>37274</v>
-      </c>
-      <c r="E32" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="58">
-        <v>202</v>
-      </c>
-      <c r="B33" s="57">
-        <v>193.4</v>
-      </c>
-      <c r="C33" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33">
-        <v>37274</v>
-      </c>
-      <c r="E33" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="56">
-        <v>202</v>
-      </c>
-      <c r="B34" s="59">
-        <v>213.3</v>
-      </c>
-      <c r="C34" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34">
-        <v>37274</v>
-      </c>
-      <c r="E34" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="58">
-        <v>64</v>
-      </c>
-      <c r="B35" s="57">
-        <v>58.2</v>
-      </c>
-      <c r="C35" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35">
-        <v>37274</v>
-      </c>
-      <c r="E35" t="s">
-        <v>76</v>
-      </c>
-      <c r="F35" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="56">
-        <v>64</v>
-      </c>
-      <c r="B36" s="59">
-        <v>68.2</v>
-      </c>
-      <c r="C36" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36">
-        <v>37274</v>
-      </c>
-      <c r="E36" t="s">
-        <v>76</v>
-      </c>
-      <c r="F36" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="58">
-        <v>98</v>
-      </c>
-      <c r="B37" s="57">
-        <v>91.9</v>
-      </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37">
-        <v>37274</v>
-      </c>
-      <c r="E37" t="s">
-        <v>76</v>
-      </c>
-      <c r="F37" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="44">
-        <v>176</v>
-      </c>
-      <c r="B38" s="59">
-        <v>200.5</v>
-      </c>
-      <c r="C38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38">
-        <v>37274</v>
-      </c>
-      <c r="E38" t="s">
-        <v>76</v>
-      </c>
-      <c r="F38" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="58">
-        <v>21</v>
-      </c>
-      <c r="B39" s="59">
-        <v>20.2</v>
-      </c>
-      <c r="C39" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39">
-        <v>37274</v>
-      </c>
-      <c r="E39" t="s">
-        <v>76</v>
-      </c>
-      <c r="F39" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="56">
-        <v>28</v>
-      </c>
-      <c r="B40" s="57">
-        <v>29.9</v>
-      </c>
-      <c r="C40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40">
-        <v>37274</v>
-      </c>
-      <c r="E40" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="58">
-        <v>116</v>
-      </c>
-      <c r="B41" s="59">
-        <v>116.3</v>
-      </c>
-      <c r="C41" t="s">
-        <v>75</v>
-      </c>
-      <c r="D41">
-        <v>37274</v>
-      </c>
-      <c r="E41" t="s">
-        <v>76</v>
-      </c>
-      <c r="F41" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="56">
-        <v>18</v>
-      </c>
-      <c r="B42" s="57">
-        <v>18.3</v>
-      </c>
-      <c r="C42" t="s">
-        <v>75</v>
-      </c>
-      <c r="D42">
-        <v>37274</v>
-      </c>
-      <c r="E42" t="s">
-        <v>76</v>
-      </c>
-      <c r="F42" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="58">
-        <v>382</v>
-      </c>
-      <c r="B43" s="59">
-        <v>381.4</v>
-      </c>
-      <c r="C43" t="s">
-        <v>75</v>
-      </c>
-      <c r="D43">
-        <v>37274</v>
-      </c>
-      <c r="E43" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="56">
-        <v>382</v>
-      </c>
-      <c r="B44" s="57">
-        <v>448.1</v>
-      </c>
-      <c r="C44" t="s">
-        <v>75</v>
-      </c>
-      <c r="D44">
-        <v>37274</v>
-      </c>
-      <c r="E44" t="s">
-        <v>76</v>
-      </c>
-      <c r="F44" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="56">
+      <c r="B83" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>75</v>
+      </c>
+      <c r="D83" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E83" t="s">
+        <v>76</v>
+      </c>
+      <c r="F83" t="s">
+        <v>77</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2455388049</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>243</v>
+      </c>
+      <c r="B84" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="C84" t="s">
+        <v>75</v>
+      </c>
+      <c r="D84" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E84" t="s">
+        <v>76</v>
+      </c>
+      <c r="F84" t="s">
+        <v>77</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2455389348</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>243</v>
+      </c>
+      <c r="B85" t="n">
+        <v>230.8</v>
+      </c>
+      <c r="C85" t="s">
+        <v>75</v>
+      </c>
+      <c r="D85" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E85" t="s">
+        <v>76</v>
+      </c>
+      <c r="F85" t="s">
+        <v>77</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2455389348</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>6</v>
+      </c>
+      <c r="B86" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C86" t="s">
+        <v>75</v>
+      </c>
+      <c r="D86" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E86" t="s">
+        <v>76</v>
+      </c>
+      <c r="F86" t="s">
+        <v>77</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2455389416</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>104</v>
+      </c>
+      <c r="B87" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="C87" t="s">
+        <v>75</v>
+      </c>
+      <c r="D87" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E87" t="s">
+        <v>76</v>
+      </c>
+      <c r="F87" t="s">
+        <v>77</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2455388696</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>104</v>
+      </c>
+      <c r="B88" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="C88" t="s">
+        <v>75</v>
+      </c>
+      <c r="D88" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E88" t="s">
+        <v>76</v>
+      </c>
+      <c r="F88" t="s">
+        <v>77</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2455388696</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
         <v>48</v>
       </c>
-      <c r="B45" s="57">
-        <v>48.6</v>
-      </c>
-      <c r="C45" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45">
-        <v>37274</v>
-      </c>
-      <c r="E45" t="s">
-        <v>76</v>
-      </c>
-      <c r="F45" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="58">
-        <v>115</v>
-      </c>
-      <c r="B46" s="59">
-        <v>126.5</v>
-      </c>
-      <c r="C46" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46">
-        <v>37274</v>
-      </c>
-      <c r="E46" t="s">
-        <v>76</v>
-      </c>
-      <c r="F46" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="56">
-        <v>14</v>
-      </c>
-      <c r="B47" s="57">
-        <v>15.5</v>
-      </c>
-      <c r="C47" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47">
-        <v>37274</v>
-      </c>
-      <c r="E47" t="s">
-        <v>76</v>
-      </c>
-      <c r="F47" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="58">
-        <v>210</v>
-      </c>
-      <c r="B48" s="59">
-        <v>194.9</v>
-      </c>
-      <c r="C48" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48">
-        <v>37274</v>
-      </c>
-      <c r="E48" t="s">
-        <v>76</v>
-      </c>
-      <c r="F48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="56">
-        <v>22</v>
-      </c>
-      <c r="B49" s="57">
-        <v>21.9</v>
-      </c>
-      <c r="C49" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49">
-        <v>37274</v>
-      </c>
-      <c r="E49" t="s">
-        <v>76</v>
-      </c>
-      <c r="F49" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="58"/>
-      <c r="B50" s="59"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="56"/>
-      <c r="B51" s="57"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="58"/>
-      <c r="B52" s="59"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="56"/>
-      <c r="B53" s="57"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="58"/>
-      <c r="B54" s="59"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="56"/>
-      <c r="B55" s="57"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="58"/>
-      <c r="B56" s="59"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="56"/>
-      <c r="B57" s="57"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="58"/>
-      <c r="B58" s="59"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="56"/>
-      <c r="B59" s="57"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="58"/>
-      <c r="B60" s="59"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" s="56"/>
-      <c r="B61" s="57"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="58"/>
-      <c r="B62" s="59"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" s="56"/>
-      <c r="B63" s="57"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="58"/>
-      <c r="B64" s="59"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="56"/>
-      <c r="B65" s="57"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="58"/>
-      <c r="B66" s="59"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="56"/>
-      <c r="B67" s="57"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="58"/>
-      <c r="B68" s="59"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="56"/>
-      <c r="B69" s="57"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="58"/>
-      <c r="B70" s="59"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="56"/>
-      <c r="B71" s="57"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="58"/>
-      <c r="B72" s="59"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="56"/>
-      <c r="B73" s="57"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="58"/>
-      <c r="B74" s="59"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="56"/>
-      <c r="B75" s="57"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="58"/>
-      <c r="B76" s="59"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="56"/>
-      <c r="B77" s="57"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="58"/>
-      <c r="B78" s="59"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="56"/>
-      <c r="B79" s="57"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="58"/>
-      <c r="B80" s="59"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="56"/>
-      <c r="B81" s="57"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="58"/>
-      <c r="B82" s="59"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="56"/>
-      <c r="B83" s="57"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="58"/>
-      <c r="B84" s="59"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="56"/>
-      <c r="B85" s="57"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="58"/>
-      <c r="B86" s="59"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="56"/>
-      <c r="B87" s="57"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" s="58"/>
-      <c r="B88" s="59"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="56"/>
-      <c r="B89" s="57"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" s="58"/>
-      <c r="B90" s="59"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="56"/>
-      <c r="B91" s="57"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" s="58"/>
-      <c r="B92" s="59"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="56"/>
-      <c r="B93" s="57"/>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" s="58"/>
-      <c r="B94" s="59"/>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="56"/>
-      <c r="B95" s="57"/>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" s="58"/>
-      <c r="B96" s="59"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="56"/>
-      <c r="B97" s="57"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="58"/>
-      <c r="B98" s="59"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="56"/>
-      <c r="B99" s="57"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" s="58"/>
-      <c r="B100" s="59"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" s="56"/>
-      <c r="B101" s="57"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" s="58"/>
-      <c r="B102" s="59"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" s="56"/>
-      <c r="B103" s="57"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" s="58"/>
-      <c r="B104" s="59"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A105" s="56"/>
-      <c r="B105" s="57"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="58"/>
-      <c r="B106" s="59"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="56"/>
-      <c r="B107" s="57"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="58"/>
-      <c r="B108" s="59"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="56"/>
-      <c r="B109" s="57"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="58"/>
-      <c r="B110" s="59"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" s="56"/>
-      <c r="B111" s="57"/>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" s="58"/>
-      <c r="B112" s="59"/>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" s="56"/>
-      <c r="B113" s="57"/>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" s="58"/>
-      <c r="B114" s="59"/>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" s="56"/>
-      <c r="B115" s="57"/>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" s="58"/>
-      <c r="B116" s="59"/>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" s="56"/>
-      <c r="B117" s="57"/>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" s="58"/>
-      <c r="B118" s="59"/>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" s="56"/>
-      <c r="B119" s="57"/>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" s="58"/>
-      <c r="B120" s="59"/>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" s="56"/>
-      <c r="B121" s="57"/>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" s="58"/>
-      <c r="B122" s="59"/>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" s="56"/>
-      <c r="B123" s="57"/>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" s="58"/>
-      <c r="B124" s="59"/>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" s="56"/>
-      <c r="B125" s="57"/>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" s="58"/>
-      <c r="B126" s="59"/>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" s="56"/>
-      <c r="B127" s="57"/>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A128" s="58"/>
-      <c r="B128" s="59"/>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" s="56"/>
-      <c r="B129" s="57"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A130" s="58"/>
-      <c r="B130" s="59"/>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A131" s="56"/>
-      <c r="B131" s="57"/>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A132" s="58"/>
-      <c r="B132" s="59"/>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A133" s="56"/>
-      <c r="B133" s="57"/>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A134" s="58"/>
-      <c r="B134" s="59"/>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A135" s="56"/>
-      <c r="B135" s="57"/>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A136" s="58"/>
-      <c r="B136" s="59"/>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A137" s="56"/>
-      <c r="B137" s="57"/>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A138" s="58"/>
-      <c r="B138" s="59"/>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" s="56"/>
-      <c r="B139" s="57"/>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" s="58"/>
-      <c r="B140" s="59"/>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" s="56"/>
-      <c r="B141" s="57"/>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A142" s="58"/>
-      <c r="B142" s="59"/>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A143" s="56"/>
-      <c r="B143" s="57"/>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A144" s="58"/>
-      <c r="B144" s="59"/>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" s="56"/>
-      <c r="B145" s="57"/>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A146" s="58"/>
-      <c r="B146" s="59"/>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A147" s="56"/>
-      <c r="B147" s="57"/>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" s="60"/>
-      <c r="B148" s="55"/>
+      <c r="B89" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="C89" t="s">
+        <v>75</v>
+      </c>
+      <c r="D89" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E89" t="s">
+        <v>76</v>
+      </c>
+      <c r="F89" t="s">
+        <v>77</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2455388702</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>44</v>
+      </c>
+      <c r="B90" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>75</v>
+      </c>
+      <c r="D90" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E90" t="s">
+        <v>76</v>
+      </c>
+      <c r="F90" t="s">
+        <v>77</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2455388867</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>44</v>
+      </c>
+      <c r="B91" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="C91" t="s">
+        <v>75</v>
+      </c>
+      <c r="D91" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E91" t="s">
+        <v>76</v>
+      </c>
+      <c r="F91" t="s">
+        <v>77</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2455388867</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>62</v>
+      </c>
+      <c r="B92" t="n">
+        <v>64.6</v>
+      </c>
+      <c r="C92" t="s">
+        <v>75</v>
+      </c>
+      <c r="D92" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E92" t="s">
+        <v>76</v>
+      </c>
+      <c r="F92" t="s">
+        <v>77</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2455388879</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>168</v>
+      </c>
+      <c r="B93" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="C93" t="s">
+        <v>75</v>
+      </c>
+      <c r="D93" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E93" t="s">
+        <v>76</v>
+      </c>
+      <c r="F93" t="s">
+        <v>77</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2455388886</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>5</v>
+      </c>
+      <c r="B94" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" t="s">
+        <v>75</v>
+      </c>
+      <c r="D94" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E94" t="s">
+        <v>76</v>
+      </c>
+      <c r="F94" t="s">
+        <v>77</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2455388888</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>70</v>
+      </c>
+      <c r="B95" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="C95" t="s">
+        <v>75</v>
+      </c>
+      <c r="D95" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E95" t="s">
+        <v>76</v>
+      </c>
+      <c r="F95" t="s">
+        <v>77</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2455388948</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>41</v>
+      </c>
+      <c r="B96" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="C96" t="s">
+        <v>75</v>
+      </c>
+      <c r="D96" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E96" t="s">
+        <v>76</v>
+      </c>
+      <c r="F96" t="s">
+        <v>77</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2455389197</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>41</v>
+      </c>
+      <c r="B97" t="n">
+        <v>42</v>
+      </c>
+      <c r="C97" t="s">
+        <v>75</v>
+      </c>
+      <c r="D97" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E97" t="s">
+        <v>76</v>
+      </c>
+      <c r="F97" t="s">
+        <v>77</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2455389197</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>11</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C98" t="s">
+        <v>75</v>
+      </c>
+      <c r="D98" t="n">
+        <v>37274</v>
+      </c>
+      <c r="E98" t="s">
+        <v>76</v>
+      </c>
+      <c r="F98" t="s">
+        <v>77</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2455389549</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>